--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0005.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0005.xlsx
@@ -911,7 +911,7 @@
           <t>…
 Không ai có thể tiếp tục gánh vác một số phận nặng nề đến thế. Nỗi bi thương dưới lòng đất khiến lòng ta đau đớn. Vì vậy, đôi cánh tượng trưng cho một hành trình dài đã gập lại, chờ đợi ngày những linh hồn đã khuất được giải thoát.
 …
-(Tờ giấy ghi chú này, với Dodget chữ nguệch ngoạc, dường như bị xé ra từ một cuốn sổ. Ai đã để lại nó ở trạm?)</t>
+(Tờ giấy ghi chú này, với nét chữ nguệch ngoạc, dường như bị xé ra từ một cuốn sổ. Ai đã để lại nó ở trạm?)</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Tất nhiên! Cảnh tượng đó đáng xem lắm. Ngớ ngẩn thật, nhưng ai mà chẳng thích một màn trình diễn hay ho. Khi chúng tôi chìm sâu vào sương mù, ta đã thoát được. Ha, cậu nên thấy mặt con bé lúc đó mới vui!</t>
+          <t>Tất nhiên! Cảnh tượng đó đáng xem lắm. Ngớ ngẩn thật, nhưng ai mà chẳng thích một màn trình diễn hay ho. Khi chúng tôi chìm sâu vào sương mù, tao đã thoát được. Ha, cậu nên thấy mặt con bé lúc đó mới vui!</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Dù sương mù nguy hiểm hay những giai điệu ma quái kia cũng chẳng lay chuyển được quyết tâm của bạn tôi! Thay vào đó, {Male=cậu ấy;Female=cô ấy} đã nhảy lên lưng con cá quái vật ấy và dẫn chúng ta thoát khỏi hiểm nguy, dũng mãnh như sư tử.</t>
+          <t>Dù sương mù nguy hiểm hay những giai điệu ma quái kia cũng chẳng lay chuyển được quyết tâm của bạn tôi! Thay vào đó, {Male=he;Female=she} đã nhảy lên lưng con cá quái vật ấy và dẫn chúng ta thoát khỏi hiểm nguy, dũng mãnh như sư tử.</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>Trở lại sân khấu, những chú Plushies tiết lộ một sự thật gây chấn động: chủ nhân của chúng chưa bao giờ bỏ rơi chúng—họ đã bị lưu đày.
-Để bảo vệ Echoes của mình khỏi Tổ Chức—những kẻ muốn xóa sổ hoàn toàn tần số của họ—chủ nhân đã phải đưa ra quyết định đau đớn là để chúng lại phía sau.
+Để bảo vệ Echo của mình khỏi Tổ Chức—những kẻ muốn xóa sổ hoàn toàn tần số của họ—chủ nhân đã phải đưa ra quyết định đau đớn là để chúng lại phía sau.
 Tại nhà hát, một số Plushies được đoàn tụ vui mừng với chủ nhân, trong khi những con khác lại tìm thấy những món đồ quý giá mà chủ nhân từng nâng niu.</t>
         </is>
       </c>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hello, {Male=anh;Female=chị} {PlayerName}. Lâu lắm rồi không gặp! Từ khi {Male=anh;Female=chị} giúp phục hồi lại đây, ngày càng nhiều Echoes đổ về Plushie Village.</t>
+          <t>Xin chào, {Male=Mr.;Female=Ms.} {PlayerName}. Lâu lắm rồi không gặp! Từ khi bạn giúp phục hồi lại đây, ngày càng nhiều Echo đổ về Làng Thú Nhồi Bông.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Cậu biết không, nó đẹp thật đấy... Nhìn xem, những vì sao cũng đang sáng lên kìa. Cậu nghĩ bên trong có gì nhỉ? Không lẽ lại là mấy con Echoes chực chờ lao ra tấn công chúng ta à?</t>
+          <t>Cậu biết không, nó đẹp thật đấy... Nhìn xem, những vì sao cũng đang sáng lên kìa. Cậu nghĩ bên trong có gì nhỉ? Không lẽ lại là mấy con Echo chực chờ lao ra tấn công chúng ta à?</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Cảm ơn {Male=anh;Female=chị} {PlayerName}! Bọn Plushies đã hỏi han xem {Male=anh;Female=chị} thích gì và mất khá lâu để chuẩn bị món quà này cho {Male=anh;Female=chị} đấy. Đến xem thử nào!</t>
+          <t>Cảm ơn bạn {PlayerName}! Bọn Plushies đã hỏi han xem bạn thích gì và mất khá lâu để chuẩn bị món quà này cho bạn đấy. Đến xem thử nào!</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Họ rất vui vì {Male=anh;Female=chị} thích nó! Nhân tiện, tôi có điều này muốn hỏi {Male=anh;Female=chị}, {Male=anh;Female=chị} {PlayerName}. {Male=Anh;Female=Chị} đã bao giờ thấy một con Seaside Cendrelis chưa?</t>
+          <t>Họ rất vui vì bạn thích nó! Nhân tiện, tôi có điều này muốn hỏi bạn, {Male=Mr.;Female=Ms.} {PlayerName}. bạn đã bao giờ thấy một con Seaside Cendrelis chưa?</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Đúng là nó... Vẻ đẹp như thế này chỉ gặp một lần trong đời. Ôi, cảm ơn {Male=anh;Female=chị} nhiều lắm, {Male=anh;Female=chị} {PlayerName}! Enzo đã thề rằng Seaside Cendrelis đã tuyệt chủng từ lâu, và tôi suýt tin là vậy cho đến tận bây giờ!</t>
+          <t>Đúng là nó... Vẻ đẹp như thế này chỉ gặp một lần trong đời. Ôi, cảm ơn bạn nhiều lắm, {Male=Mr.;Female=Ms.} {PlayerName}! Enzo đã thề rằng Seaside Cendrelis đã tuyệt chủng từ lâu, và tôi suýt tin là vậy cho đến tận bây giờ!</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Đội Thú Nhồi Bông của chúng ta, tập hợp những Resonator Echoes xuất sắc nhất, đã háo hức chờ đợi một chuyến phiêu lưu mới kể từ khi Plushie Village hồi sinh từ đống tro tàn!</t>
+          <t>Đội Thú Nhồi Bông của chúng ta, tập hợp những Cộng Hưởng Giả Echo xuất sắc nhất, đã háo hức chờ đợi một chuyến phiêu lưu mới kể từ khi Làng Thú Nhồi Bông hồi sinh từ đống tro tàn!</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Năng lượng Quá Tải này cuối cùng sẽ biến thành những mảnh ký ức vương vãi trong Tòa Tower Ngược này. Ta đã từng thử thu thập những "mảnh vỡ" ấy trước đây.</t>
+          <t>Năng lượng Quá Tải này cuối cùng sẽ biến thành những mảnh ký ức vương vãi trong Tòa Tháp Ngược này. Ta đã từng thử thu thập những "mảnh vỡ" ấy trước đây.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Gần đây ta cảm nhận được một đợt sóng tần số mạnh từ tháp này, nên mới đến xem xét. Hóa ra là cậu đã giải thoát mấy đứa trẻ bị giam cầm này.</t>
+          <t>Gần đây tao cảm nhận được một đợt sóng tần số mạnh từ tháp này, nên mới đến xem xét. Hóa ra là cậu đã giải thoát mấy đứa trẻ bị giam cầm này.</t>
         </is>
       </c>
     </row>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Night Tưởng Niệm đã khép lại trong viên mãn, thị trấn dần trở lại nhịp sống yên bình thường nhật. Cối xay gió kẽo kẹt quay, lá cây lững lờ trôi trong làn gió đêm. 
+          <t>Đêm Tưởng Niệm đã khép lại trong viên mãn, thị trấn dần trở lại nhịp sống yên bình thường nhật. Cối xay gió kẽo kẹt quay, lá cây lững lờ trôi trong làn gió đêm. 
 Cảm giác như chẳng có gì xảy ra, như thể tất cả chỉ là một giấc mơ thoáng qua trong đêm. Nhưng cậu biết điều đó là thật, bởi Cantarella vẫn đang đứng ngay bên cạnh cậu.</t>
         </is>
       </c>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Khi cậu cầm con búp bê lên, những đường Dodget của nó bỗng trở nên sắc Dodget và sống động. Lông mày thanh tú, đôi mắt sáng ngời, bộ trang phục trang nhã như bừng tỉnh chỉ trong nháy mắt.</t>
+          <t>Khi cậu cầm con búp bê lên, những đường nét của nó bỗng trở nên sắc nét và sống động. Lông mày thanh tú, đôi mắt sáng ngời, bộ trang phục trang nhã như bừng tỉnh chỉ trong nháy mắt.</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Night Tưởng Niệm là lễ hội thường niên ở Thị trấn Egla, nhằm tưởng nhớ những người đã khuất. Khi màn đêm buông xuống, mọi người hóa trang thành hồn ma và tham gia đủ các hoạt động.</t>
+          <t>Đêm Tưởng Niệm là lễ hội thường niên ở Thị trấn Egla, nhằm tưởng nhớ những người đã khuất. Khi màn đêm buông xuống, mọi người hóa trang thành hồn ma và tham gia đủ các hoạt động.</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Sea Apple vốn nổi tiếng có độc. Manh mối này chắc chắn là chìa khóa để giải câu đố về Quả Táo Đỏ. 
+          <t>Táo Biển vốn nổi tiếng có độc. Manh mối này chắc chắn là chìa khóa để giải câu đố về Quả Táo Đỏ. 
 Trước khi cậu kịp hỏi thêm gì, cô bé đã chạy vụt đi chỗ khác.</t>
         </is>
       </c>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Quả Sea Apple đỏ thẫm, còn gọi là "kẻ quyến rũ tử thần", là một loài thực vật nguy hiểm. Chỉ cần một miếng cắn cũng đủ khiến nạn nhân tê liệt, ngạt thở, hoặc chịu đựng cơn đau như cổ họng bị thiêu đốt, nội tạng rách nát—cuối cùng dẫn đến cái chết đau đớn.</t>
+          <t>Quả Táo Biển đỏ thẫm, còn gọi là "kẻ quyến rũ tử thần", là một loài thực vật nguy hiểm. Chỉ cần một miếng cắn cũng đủ khiến nạn nhân tê liệt, ngạt thở, hoặc chịu đựng cơn đau như cổ họng bị thiêu đốt, nội tạng rách nát—cuối cùng dẫn đến cái chết đau đớn.</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Còn về câu đố đầu tiên, "Song Nữ Thần," "vương miện trên đỉnh núi" và "thác nước đổ xuống vực sâu" rõ ràng chỉ về nơi này—một lâu đài như vương miện nằm trên vách đá gồ ghề, với dòng thác ào ạt chảy xuống.</t>
+          <t>Còn về câu đố đầu tiên, "Khúc Ca Nữ Thần," "vương miện trên đỉnh núi" và "thác nước đổ xuống vực sâu" rõ ràng chỉ về nơi này—một lâu đài như vương miện nằm trên vách đá gồ ghề, với dòng thác ào ạt chảy xuống.</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Máu và nước mắt đổ xuống trong những thử thách qua bao năm tháng đã thấm đẫm lâu đài này, hòa quyện thành thứ mà giờ đây chúng ta gọi là &lt;ano=Sonoro Sphere&gt;Sea of Ghosts&lt;/ano&gt;.</t>
+          <t>Máu và nước mắt đổ xuống trong những thử thách qua bao năm tháng đã thấm đẫm lâu đài này, hòa quyện thành thứ mà giờ đây chúng ta gọi là &lt;ano=Sonoro Sphere&gt;Biển Ma&lt;/ano&gt;.</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Ta đã chứng kiến ngươi thanh tẩy hỗn loạn của Inverted Tower, khôi phục trật tự cho trời cao và biển rộng. Nếu ngươi là người phán xét cuối cùng cho ta... đó sẽ là vinh dự lớn nhất.</t>
+          <t>Ta đã chứng kiến ngươi thanh tẩy hỗn loạn của Tháp Đảo Ngược, khôi phục trật tự cho trời cao và biển rộng. Nếu ngươi là người phán xét cuối cùng cho ta... đó sẽ là vinh dự lớn nhất.</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Một câu chuyện ly kỳ, cậu thấy thế nào? Like thưởng thức miếng thịt cừu tái vừa chín tới, ăn kèm hàu. Chỉ cần một lát cắt nhẹ, nước sốt đỏ au trào ra, tô điểm thêm hương vị cho món ăn vốn đã tuyệt hảo.</t>
+          <t>Một câu chuyện ly kỳ, cậu thấy thế nào? Giống như thưởng thức miếng thịt cừu tái vừa chín tới, ăn kèm hàu. Chỉ cần một lát cắt nhẹ, nước sốt đỏ au trào ra, tô điểm thêm hương vị cho món ăn vốn đã tuyệt hảo.</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Oh, sorry. Nếu làm cậu khó chịu thì bỏ qua nhé. Đó là một bài dân ca cũ về Night Tưởng Nhớ. Người ta bảo giai điệu ma mị của nó có một tần số kỳ lạ, có thể thu hút sự chú ý của những "con quỷ" đói khát.</t>
+          <t>Ồ, xin lỗi. Nếu làm cậu khó chịu thì bỏ qua nhé. Đó là một bài dân ca cũ về Đêm Tưởng Nhớ. Người ta bảo giai điệu ma mị của nó có một tần số kỳ lạ, có thể thu hút sự chú ý của những "con quỷ" đói khát.</t>
         </is>
       </c>
     </row>
@@ -7730,7 +7730,7 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>Bạn nhận được tin nhắn kỳ lạ từ một "cô bé ma". Tần số méo mó trong đó ảnh hưởng đến cả bạn và Abby. 
-Để khám phá bí ẩn và hóa giải tác động, bạn quyết định tham dự Night Tưởng Niệm ở Thị trấn Egla, như lời nhắn đề cập.</t>
+Để khám phá bí ẩn và hóa giải tác động, bạn quyết định tham dự Đêm Tưởng Niệm ở Thị trấn Egla, như lời nhắn đề cập.</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Người hướng dẫn giải thích cho cậu về Night Tưởng Niệm. Đây là lễ hội hàng năm ở thị trấn Egla, để tưởng nhớ những người đã khuất. Mọi người sẽ hóa trang thành ma quỷ vào ban đêm và tham gia nhiều hoạt động.
+          <t>Người hướng dẫn giải thích cho cậu về Đêm Tưởng Niệm. Đây là lễ hội hàng năm ở thị trấn Egla, để tưởng nhớ những người đã khuất. Mọi người sẽ hóa trang thành ma quỷ vào ban đêm và tham gia nhiều hoạt động.
 Người hướng dẫn bảo cậu phải đeo mặt nạ, và cậu đưa ra chiếc mặt nạ của Nhà Học Giả, vừa vặn hoàn hảo.</t>
         </is>
       </c>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Khi Cantarella ngươi mò với chiếc hộp nhạc, cậu nhận thấy hình dáng của nó giống một quả táo.
+          <t>Khi Cantarella mày mò với chiếc hộp nhạc, cậu nhận thấy hình dáng của nó giống một quả táo.
 Nhờ gợi ý của cậu, cô giải được câu đố đầu tiên và dẫn cậu đến gian hàng thứ hai.</t>
         </is>
       </c>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Khi hộp nhạc vang lên, con búp bê đội mũ đỏ hiện ra và nhảy múa, rồi đột ngột dừng lại. Cậu nhận ra đó chỉ là ảo ảnh, nhưng âm nhạc gợi nhớ đến Porto-Veno Castle. Một bóng tối thoáng qua trên gương mặt thường điềm tĩnh của Cantarella.
+          <t>Khi hộp nhạc vang lên, con búp bê đội mũ đỏ hiện ra và nhảy múa, rồi đột ngột dừng lại. Cậu nhận ra đó chỉ là ảo ảnh, nhưng âm nhạc gợi nhớ đến Lâu Đài Porto-Veno. Một bóng tối thoáng qua trên gương mặt thường điềm tĩnh của Cantarella.
 Một cơn đau đầu nhói ngắt quãng suy nghĩ của cậu, những tần số méo mó ngày càng dữ dội. Cậu nắm lấy cơ hội và hỏi Cantarella liệu có thể nghỉ ngơi tại lâu đài của cô ấy không, và cô đồng ý.</t>
         </is>
       </c>
@@ -8472,7 +8472,7 @@
       <c r="M121" t="inlineStr">
         <is>
           <t>Cô bé chỉ tay vào một loài thực vật màu đỏ thẫm gần đó. Hình dáng nó giống quả táo, nhưng lại trông như một sinh vật biển kỳ lạ.
-Bạn nhận ra đó là Sea Apple độc, có thể là chìa khóa để giải câu đố về Quả Táo Đỏ.
+Bạn nhận ra đó là Táo Biển độc, có thể là chìa khóa để giải câu đố về Quả Táo Đỏ.
 Trước khi bạn kịp hỏi han, cô bé đã chạy đi một góc khác của khu vườn.</t>
         </is>
       </c>
@@ -8677,8 +8677,8 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>Cậu theo cô bé đến góc phố và thấy Cantarella đang nhảy múa, những bước chân như điều chỉnh một loại tần số nào đó.
-Cậu chia sẻ suy nghĩ của mình, và cô ấy thừa nhận "cô gái ma" ám chỉ những Thử Thách Thần Linh tàn nhẫn của gia tộc Fisalia. Máu và nước mắt từ những thử thách ấy đã bóp méo Porto-Veno Castle thành &lt;ano=Sonoro Sphere&gt;Sea of Ghosts&lt;/ano&gt;.
-Để vén màn sự thật và phá bỏ "lời nguyền" trói buộc cậu, cậu phải lặn sâu vào Sea of Ghosts này.</t>
+Cậu chia sẻ suy nghĩ của mình, và cô ấy thừa nhận "cô gái ma" ám chỉ những Thử Thách Thần Linh tàn nhẫn của gia tộc Fisalia. Máu và nước mắt từ những thử thách ấy đã bóp méo Porto-Veno Castle thành &lt;ano=Sonoro Sphere&gt;Biển Ma&lt;/ano&gt;.
+Để vén màn sự thật và phá bỏ "lời nguyền" trói buộc cậu, cậu phải lặn sâu vào Biển Ma này.</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8810,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Night Tưởng Nhớ kết thúc êm đẹp, các cô gái trở về nhà. Ảnh hưởng còn vương vấn trên cậu và Abby cũng tan biến, mọi thứ trở lại bình yên như thường.
+          <t>Đêm Tưởng Nhớ kết thúc êm đẹp, các cô gái trở về nhà. Ảnh hưởng còn vương vấn trên cậu và Abby cũng tan biến, mọi thứ trở lại bình yên như thường.
 Cảm giác như chẳng có gì xảy ra, như thể chỉ là một giấc mơ thoáng qua trong đêm. Nhưng cậu biết đó là thật, vì Cantarella vẫn đứng ngay bên cạnh.
 Nàng thừa nhận cậu mạnh hơn mình, nhưng điều đó không ngăn được bản năng muốn chăm sóc cậu. Nàng mời cậu nghỉ ngơi tại lâu đài giờ đây đã bình yên của mình.</t>
         </is>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Nhiều năm trước, Cantarella đã dùng ảo ảnh lừa dối tộc trưởng Fisalia lúc bấy giờ, chiếm lấy vị trí của ông ta và chấm dứt những thử thách tàn khốc. Nhưng nỗi ám ảnh còn sót lại của hắn, bị những lời thì thầm tha hóa, vẫn vương vấn trong lâu đài, biến nơi đây thành Sea of Ghosts.
+          <t>Nhiều năm trước, Cantarella đã dùng ảo ảnh lừa dối tộc trưởng Fisalia lúc bấy giờ, chiếm lấy vị trí của ông ta và chấm dứt những thử thách tàn khốc. Nhưng nỗi ám ảnh còn sót lại của hắn, bị những lời thì thầm tha hóa, vẫn vương vấn trong lâu đài, biến nơi đây thành Biển Ma.
 Cùng với Cantarella, ngươi đã giải thoát cho ý chí còn vương vấn của hắn.</t>
         </is>
       </c>
@@ -9282,7 +9282,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Khi ám ảnh dai dẳng của vị tộc trưởng Fisalias quá cố dần tan biến, Sea of Ghosts cũng biến mất.
+          <t>Khi ám ảnh dai dẳng của vị tộc trưởng Fisalias quá cố dần tan biến, Biển Ma cũng biến mất.
 Giữa những khúc thánh ca vang lên xung quanh, cậu thấy mình đang ở trong điện thờ, nơi những cô gái đáng lẽ đã chết đứng trước mặt, tất cả đều an toàn vô sự.</t>
         </is>
       </c>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tôi không hề có ý lôi kéo cậu vào chuyện này. Tôi định một mình gánh vác tất cả. Đó là lý do tại sao năm nay, tôi tự mình tham gia Night Tưởng Niệm, và với tư cách chủ trì, tôi đã chọn chủ đề "những cô gái ma".</t>
+          <t>Tôi không hề có ý lôi kéo cậu vào chuyện này. Tôi định một mình gánh vác tất cả. Đó là lý do tại sao năm nay, tôi tự mình tham gia Đêm Tưởng Niệm, và với tư cách chủ trì, tôi đã chọn chủ đề "những cô gái ma".</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Kế hoạch của ta là đột phá qua Sea of Ghosts, tuyên bố đã giải được câu đố và giành được thuốc hồi sinh, rồi dùng nó để đưa các cô gái về nhà khi Dance Tử Thần bắt đầu vào nửa đêm.</t>
+          <t>Kế hoạch của ta là đột phá qua Biển Ma, tuyên bố đã giải được câu đố và giành được thuốc hồi sinh, rồi dùng nó để đưa các cô gái về nhà khi Vũ Điệu Tử Thần bắt đầu vào nửa đêm.</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Khi nhìn thấy bức thư đó và cảm nhận điều bất thường nơi cậu, ta biết cậu không thể đứng ngoài việc này được nữa. Với thể chất đặc biệt, cậu đã bị ảnh hưởng bởi những tần số tràn ra từ Sea of Ghosts.</t>
+          <t>Khi nhìn thấy bức thư đó và cảm nhận điều bất thường nơi cậu, ta biết cậu không thể đứng ngoài việc này được nữa. Với thể chất đặc biệt, cậu đã bị ảnh hưởng bởi những tần số tràn ra từ Biển Ma.</t>
         </is>
       </c>
     </row>
@@ -9742,8 +9742,8 @@
       <c r="M140" t="inlineStr">
         <is>
           <t>Bạn nghe Cantarella kể rằng kể từ khi sự dối trá của Threnodian bị phơi bày, tần số và tình hình quanh Ragunna đã thay đổi. Đã đến lúc các cô gái cuối cùng cũng được về nhà.
-Cô thừa nhận chưa bao giờ định lôi bạn vào chuyện này và dự định tự mình giải quyết tất cả. Đó là lý do trong Night Tưởng Niệm năm nay, cô đích thân tham gia và chọn chủ đề "những cô gái ma".
-Cô định một mình lặn xuống Sea of Ghosts, giả vờ đã giải được câu đố và lấy được thuốc hồi sinh. Nhờ vậy, cô có thể đưa các cô gái về nhà trong Điệu Nhảy Của Người Chết lúc nửa đêm.
+Cô thừa nhận chưa bao giờ định lôi bạn vào chuyện này và dự định tự mình giải quyết tất cả. Đó là lý do trong Đêm Tưởng Niệm năm nay, cô đích thân tham gia và chọn chủ đề "những cô gái ma".
+Cô định một mình lặn xuống Biển Ma, giả vờ đã giải được câu đố và lấy được thuốc hồi sinh. Nhờ vậy, cô có thể đưa các cô gái về nhà trong Điệu Nhảy Của Người Chết lúc nửa đêm.
 Nhưng tin nhắn của Annis đã đưa bạn đến bên cô để hoàn thành kế hoạch.</t>
         </is>
       </c>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Cố gắng tốt lắm, nhưng đây không phải giếng ước đâu, huống chi lại liều lĩnh ước nguyện với Sea of Ghosts.
+          <t>Cố gắng tốt lắm, nhưng đây không phải giếng ước đâu, huống chi lại liều lĩnh ước nguyện với Biển Ma.
 Vực thẳm dường như không hứng thú nuốt chửng cậu lúc này và trả lại Shell Credit cho cậu.</t>
         </is>
       </c>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Cậu và Cantarella bước vào Lâu đài Porto-Veno, nơi giờ đây trông đã khác lạ.
+          <t>Cậu và Cantarella bước vào Porto-Veno Castle, nơi giờ đây trông đã khác lạ.
 Cantarella giải thích rằng những tần số méo mó đã nhấn chìm nơi này, pha trộn quá khứ và tương lai.
 Cô cố gắng giữ lại tia sáng cuối cùng trong vực tối này và cất nó vào chiếc đèn.</t>
         </is>
@@ -10283,7 +10283,7 @@
       <c r="M148" t="inlineStr">
         <is>
           <t>Bạn tìm thấy thông báo về kỳ Divine Trials trước đó.
-Thử thách đầu tiên yêu cầu người tham gia chọn ra ba quả Sea Apple độc nhất từ vực sâu và mang chúng về bằng mọi giá.
+Thử thách đầu tiên yêu cầu người tham gia chọn ra ba quả Táo Biển độc nhất từ vực sâu và mang chúng về bằng mọi giá.
 Có vẻ như những tần số méo mó muốn các bạn tự mình trải nghiệm các thử thách để khám phá bí ẩn về "cô gái ma".</t>
         </is>
       </c>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy Quả Sea Apple đầu tiên cùng một bức thư của cô gái tên Chloe, người đang lo lắng.
+          <t>Bạn tìm thấy Quả Táo Biển đầu tiên cùng một bức thư của cô gái tên Chloe, người đang lo lắng.
 Thử Thách Thần Thánh là truyền thống thiêng liêng của gia tộc Fisalia, nhưng hiểm nguy xung quanh đã khiến một số thành viên tìm đến những thường dân giống con gái họ, dùng họ làm vật thế thân.</t>
         </is>
       </c>
@@ -10417,7 +10417,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy Quả Sea Apple thứ hai và một bức thư khác của Chloe, ghi lại lý do và cách cô tham gia thử thách.
+          <t>Bạn tìm thấy Quả Táo Biển thứ hai và một bức thư khác của Chloe, ghi lại lý do và cách cô tham gia thử thách.
 Để tránh con mắt dòm ngó, các cô gái lập những thỏa thuận bí mật qua lời thì thầm, như "ngân nga giai điệu đặc biệt", "dùng màu sắc phù hợp", "gõ cửa ba lần mỗi hai giây"…</t>
         </is>
       </c>
@@ -10485,7 +10485,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Bạn tìm thấy Quả Sea Apple thứ ba và một bức thư khác của Chloe, tiết lộ sự thay đổi trong suy nghĩ của cô trong suốt thử thách.
+          <t>Bạn tìm thấy Quả Táo Biển thứ ba và một bức thư khác của Chloe, tiết lộ sự thay đổi trong suy nghĩ của cô trong suốt thử thách.
 Gia tộc Fisalia được xây dựng trên nọc độc, và từ nhỏ, mỗi đứa trẻ Fisalia đều được tiếp xúc với nó, học cách chống chịu.
 Dòng máu Fisalia có thể phát triển khả năng liên quan đến độc khi tiếp xúc với chất độc và bị đẩy đến bờ vực, nhưng thường dân hiếm khi sống sót. Thế nhưng, một cô gái thường dân tên Annis dường như cũng đã đánh thức khả năng ấy, dù cổ họng cô bị tổn thương vì độc, khiến cô vĩnh viễn không thể cất tiếng.</t>
         </is>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Tĩnh lặng, bóng tối và im lìm. "Fail", và ngươi sẽ lạc trong bóng tối. "Thành công", và ngươi sẽ đối mặt với một bóng tối còn lớn hơn.
+          <t>Tĩnh lặng, bóng tối và im lìm. "Thất bại", và ngươi sẽ lạc trong bóng tối. "Thành công", và ngươi sẽ đối mặt với một bóng tối còn lớn hơn.
 Trước nọc độc tàn nhẫn, chẳng có kẻ chiến thắng nào cả.</t>
         </is>
       </c>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Đây là thông báo thứ hai về Trial Thần Thánh.
+          <t>Đây là thông báo thứ hai về Thử Thách Thần Thánh.
 Trong thử thách thứ hai, các thí sinh cần lập đội hai người, bắt được loài sứa độc nhất, rồi trao đổi con mồi với đồng đội. Người sống sót sau nọc độc của sứa sẽ được tuyên bố chiến thắng.
 Vì trong lâu đài chỉ có cậu và Cantarella, hai người quyết định hợp tác và tìm kiếm Jellyrose Medusa.</t>
         </is>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Cuối đường hầm, ngươi và Zani phát hiện ra những cư dân bị Talos bắt đi. Dù bất tỉnh, nhưng không ai bị thương nặng. Hubert giải thích động cơ của Talos: Hắn ta định trốn khỏi Hẻm Đen trước khi ngươi kịp đến.</t>
+          <t>Cuối đường hầm, ngươi và Zani phát hiện ra những cư dân bị Talos bắt đi. Dù bất tỉnh, nhưng không ai bị thương nặng. Hubert giải thích động cơ của Talos: She was planning on escaping Black Alley before you could reach her.</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Trên đường phố Ragunna, cậu bắt gặp một nhóm trộm tự xưng là thành viên của "Ngõ Đen". Trước khi kịp truy đuổi, Zani xuất hiện và chặn đứng bọn chúng. Cô đề nghị áp giải bọn trộm đến Phòng Discipline cùng các Tuần Đạo đang tuần tra và làm báo cáo. Trong khi đó, cậu quyết định ở lại điều tra một người bí ẩn đang kêu cứu.</t>
+          <t>Trên đường phố Ragunna, cậu bắt gặp một nhóm trộm tự xưng là thành viên của "Ngõ Đen". Trước khi kịp truy đuổi, Zani xuất hiện và chặn đứng bọn chúng. Cô đề nghị áp giải bọn trộm đến Phòng Kỷ Luật cùng các Tuần Đạo đang tuần tra và làm báo cáo. Trong khi đó, cậu quyết định ở lại điều tra một người bí ẩn đang kêu cứu.</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Sau đó, Phòng Discipline cuối cùng cũng bắt được những kẻ đứng sau—chúng bị trói gô sẵn sàng trên khay. Đó là lúc Black Alley bị triệt hạ.</t>
+          <t>Sau đó, Phòng Kỷ Luật cuối cùng cũng bắt được những kẻ đứng sau—chúng bị trói gô sẵn sàng trên khay. Đó là lúc Black Alley bị triệt hạ.</t>
         </is>
       </c>
     </row>
@@ -12073,7 +12073,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Cậu tỉnh giấc giữa đêm khuya và khó lòng chợp mắt lại, nên quyết định đi dạo. Ngạc nhiên thay, cậu gặp Zani, người cũng đang vật lộn với cơn mất ngủ. Trong lúc trò chuyện, cậu phát hiện ra danh tính thật của cô ấy – Kẻ Lang Thang Night Lửa. Zani chính là người từng đánh bại băng đảng hùng mạnh đó.</t>
+          <t>Cậu tỉnh giấc giữa đêm khuya và khó lòng chợp mắt lại, nên quyết định đi dạo. Ngạc nhiên thay, cậu gặp Zani, người cũng đang vật lộn với cơn mất ngủ. Trong lúc trò chuyện, cậu phát hiện ra danh tính thật của cô ấy – Kẻ Lang Thang Đêm Lửa. Zani chính là người từng đánh bại băng đảng hùng mạnh đó.</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Người cầu cứu bí ẩn, Colleen, thừa nhận cô đến từ Black Alley—nơi từng là mái ấm của những kẻ vô gia cư, nhưng giờ đã bị Talos và băng đảng của hắn chiếm đoạt. Colleen cảnh báo rằng Talos đang sở hữu một Terminal có nguồn gốc không rõ. Cả cậu và Zani đều quyết tâm ngăn hắn lợi dụng sức mạnh của nó.</t>
+          <t>Người cầu cứu bí ẩn, Colleen, thừa nhận cô đến từ Black Alley—nơi từng là mái ấm của những kẻ vô gia cư, nhưng giờ đã bị Talos và băng đảng của hắn chiếm đoạt. Colleen cảnh báo rằng Talos đang sở hữu một Thiết bị đầu cuối có nguồn gốc không rõ. Cả cậu và Zani đều quyết tâm ngăn hắn lợi dụng sức mạnh của nó.</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12463,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Sau khi đánh bại bọn côn đồ đeo mặt nạ, chúng tiết lộ lối vào Hẻm Đen đã bị một người phụ nữ tàn nhẫn phá hủy từ vài tuần trước. Zani hộ tống chúng đến Phòng Discipline và sẽ liên lạc với cậu vào ngày hôm sau.</t>
+          <t>Sau khi đánh bại bọn côn đồ đeo mặt nạ, chúng tiết lộ lối vào Hẻm Đen đã bị một người phụ nữ tàn nhẫn phá hủy từ vài tuần trước. Zani hộ tống chúng đến Phòng Kỷ Luật và sẽ liên lạc với cậu vào ngày hôm sau.</t>
         </is>
       </c>
     </row>
@@ -17993,7 +17993,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Huaxu Academy đã nghiên cứu Feilian Beringal suốt nhiều năm và gần đây đã chia sẻ kết quả với chúng ta. Chúng ta kết hợp với dữ liệu của riêng mình và tái hiện lại tình huống mà cậu thấy đây.</t>
+          <t>Học viện Huaxu đã nghiên cứu Feilian Beringal suốt nhiều năm và gần đây đã chia sẻ kết quả với chúng ta. Chúng ta kết hợp với dữ liệu của riêng mình và tái hiện lại tình huống mà cậu thấy đây.</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đây chính là điều ta muốn nói với cậu! Cậu thử nộp một Cỗ Hòm Sonance xem? Chúng ta cần xác nhận liệu những cái từ Septimont có thể cung cấp năng lượng cho các bức tranh Morph không.</t>
+          <t>Đây chính là điều tao muốn nói với cậu! Cậu thử nộp một Cỗ Hòm Sonance xem? Chúng ta cần xác nhận liệu những cái từ Septimont có thể cung cấp năng lượng cho các bức tranh Morph không.</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Sách kể về Fabius, Hero of Heroes, chiến đấu bên cạnh Sentinel Imperator để ngăn chặn Dark Tide. Những dòng chữ ấy thật sự lay động lòng người. Bức tượng này chính là minh chứng hoàn hảo cho những chiến công vĩ đại của Fabius.</t>
+          <t>Sách kể về Fabius, Anh Hùng Trong Các Anh Hùng, chiến đấu bên cạnh Sentinel Imperator để ngăn chặn Dark Tide. Những dòng chữ ấy thật sự lay động lòng người. Bức tượng này chính là minh chứng hoàn hảo cho những chiến công vĩ đại của Fabius.</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Chẳng phải quý cô này cũng là một Gladiator đáng gờm sao? Hello, tôi là Slovik, vừa được Black Shores cử đến làm việc tại Dark Tide Observation Tower trên dãy Border Mountains.</t>
+          <t>Chẳng phải quý cô này cũng là một Gladiator đáng gờm sao? Xin chào, tôi là Slovik, vừa được Black Shores cử đến làm việc tại Dark Tide Observation Tower trên dãy Border Mountains.</t>
         </is>
       </c>
     </row>
@@ -19163,7 +19163,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tình yêu của ta dành cho Septimont ngày càng sâu đậm, nhất là khi nghiên cứu tại Tower Quan sát đang tiến triển thuận lợi. Đồng thời, ta cũng nhận ra sự đáng sợ của Dark Tide.</t>
+          <t>Tình yêu của ta dành cho Septimont ngày càng sâu đậm, nhất là khi nghiên cứu tại Tháp Quan sát đang tiến triển thuận lợi. Đồng thời, ta cũng nhận ra sự đáng sợ của Dark Tide.</t>
         </is>
       </c>
     </row>
@@ -19553,7 +19553,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Hồi nhỏ, ta đã bị cuốn hút bởi lịch sử đầy biến động của Septimont. Ta mong mọi du khách đến đây đều có thể hiểu về khoảng thời gian khó khăn và đẫm máu, nhưng cũng vô cùng hào hùng ấy—nơi thể hiện tinh thần bất khuất của dân tộc ta!</t>
+          <t>Hồi nhỏ, tao đã bị cuốn hút bởi lịch sử đầy biến động của Septimont. Tao mong mọi du khách đến đây đều có thể hiểu về khoảng thời gian khó khăn và đẫm máu, nhưng cũng vô cùng hào hùng ấy—nơi thể hiện tinh thần bất khuất của dân tộc ta!</t>
         </is>
       </c>
     </row>
@@ -19683,7 +19683,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>"Thủy triều độc tràn ngập đỉnh núi, rồng thiêng gào khóc trong đau thương, thân hình tiều tụy phủ bóng u ám lên mảnh đất này." Tôi đọc được câu này trong một cuốn sách của tổ tiên. Nó kể lại việc họ phát hiện ra Mộ Dragon Tro Tàn.</t>
+          <t>"Thủy triều độc tràn ngập đỉnh núi, rồng thiêng gào khóc trong đau thương, thân hình tiều tụy phủ bóng u ám lên mảnh đất này." Tôi đọc được câu này trong một cuốn sách của tổ tiên. Nó kể lại việc họ phát hiện ra Mộ Rồng Tro Tàn.</t>
         </is>
       </c>
     </row>
@@ -19878,7 +19878,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>À, Nhà vô địch, đã đến lúc chụp lại sự hủy hoại của Mournfell Canyon do Dark Tide gây ra. Tiếp theo, chúng ta phải ghé qua &lt;color=Highlight&gt;Tượng Đài Anh Hùng Fabius&lt;/color&gt;.</t>
+          <t>À, Nhà vô địch, đã đến lúc chụp lại sự hủy hoại của Hẻm Núi Mournfell do Dark Tide gây ra. Tiếp theo, chúng ta phải ghé qua &lt;color=Highlight&gt;Tượng Đài Anh Hùng Fabius&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Không phải ta đâu. Ta cũng chẳng biết ai làm ra chúng luôn. Bọn người chơi như tụi ta chỉ đoán là mấy fan cuồng quá nôn nóng muốn kéo người mới vào, nên... hơi quá tay một chút.</t>
+          <t>Không phải tao đâu. Tao cũng chẳng biết ai làm ra chúng luôn. Bọn người chơi như tụi tao chỉ đoán là mấy fan cuồng quá nôn nóng muốn kéo người mới vào, nên... hơi quá tay một chút.</t>
         </is>
       </c>
     </row>
@@ -20593,7 +20593,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Với thành tựu này, cậu đã trở thành đấu sĩ đầu tiên trong lịch sử Peaks of Prestige giành được cả năm Huy chương Prestige! Điều đó có nghĩa là cậu chính thức đủ tư cách thách đấu vị Lãnh chúa Prestige thứ sáu—Kẻ Chinh Phục Prestige!</t>
+          <t>Với thành tựu này, cậu đã trở thành đấu sĩ đầu tiên trong lịch sử Peaks of Prestige giành được cả năm Huy chương Uy Tín! Điều đó có nghĩa là cậu chính thức đủ tư cách thách đấu vị Lãnh chúa Uy Tín thứ sáu—Kẻ Chinh Phục Uy Tín!</t>
         </is>
       </c>
     </row>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Với thành tựu này, cậu đã trở thành đấu sĩ đầu tiên trong lịch sử Peaks of Prestige giành được cả năm Huy chương Prestige! Điều đó có nghĩa là cậu chính thức đủ tư cách thách đấu vị Lãnh chúa Prestige thứ sáu—Kẻ Chinh Phục Prestige!</t>
+          <t>Với thành tựu này, cậu đã trở thành đấu sĩ đầu tiên trong lịch sử Peaks of Prestige giành được cả năm Huy chương Uy Tín! Điều đó có nghĩa là cậu chính thức đủ tư cách thách đấu vị Lãnh chúa Uy Tín thứ sáu—Kẻ Chinh Phục Uy Tín!</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Đúng như ta dự đoán, chính ngươi đã giành chiến thắng cuối cùng! Chúc mừng, {Male=Ngài;Female=Nữ sĩ} {PlayerName}! Ngươi đã chính thức có quyền bước vào Colosseum Olymdos.</t>
+          <t>Đúng như ta dự đoán, chính ngươi đã giành chiến thắng cuối cùng! Chúc mừng, {Male=Mr.;Female=Ms.} {PlayerName}! Ngươi đã chính thức có quyền bước vào Đấu Trường Olymdos.</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Ta từng mơ tạo ra một nơi mà mọi người có thể đơn thuần tận hưởng niềm vui chiến đấu, không vết thương, không áp lực nhà tài trợ, hay những hệ lụy thắng bại thực sự trên đấu trường...</t>
+          <t>Tao từng mơ tạo ra một nơi mà mọi người có thể đơn thuần tận hưởng niềm vui chiến đấu, không vết thương, không áp lực nhà tài trợ, hay những hệ lụy thắng bại thực sự trên đấu trường...</t>
         </is>
       </c>
     </row>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Dù tổ chức trận chung kết ở Colosseum Olymdos đã thu hút rất nhiều sự chú ý, nhưng có lẽ vì mọi người vẫn chưa hiểu rõ về trò chơi này... số lượng đấu thủ mới gia nhập không được như mong đợi của ta.</t>
+          <t>Dù tổ chức trận chung kết ở Đấu Trường Olymdos đã thu hút rất nhiều sự chú ý, nhưng có lẽ vì mọi người vẫn chưa hiểu rõ về trò chơi này... số lượng đấu thủ mới gia nhập không được như mong đợi của tao.</t>
         </is>
       </c>
     </row>
@@ -21243,7 +21243,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Ta nghĩ ta đã hiểu rồi, Master. Cuộc đời như một trận chiến, phải không ạ? Phải nhìn ra bức tranh lớn, biết khi nào tấn công, khi nào rút lui... để tự rèn đúc vận mệnh của mình!</t>
+          <t>Ta nghĩ ta đã hiểu rồi, Sư phụ. Cuộc đời như một trận chiến, phải không ạ? Phải nhìn ra bức tranh lớn, biết khi nào tấn công, khi nào rút lui... để tự rèn đúc vận mệnh của mình!</t>
         </is>
       </c>
     </row>
@@ -21318,17 +21318,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Bản thảo quảng cáo&lt;/b&gt;
-&lt;s&gt;Chơi Peaks of Prestige giúp tăng trí thông minh&lt;/s&gt;
-Ghi chú: Quảng cáo sai sự thật.
-Vô số Echoes. Chiến thuật vô hạn. Bạn có thể trở thành đấu thủ đỉnh cao tiếp theo!
-Ghi chú: Tôi sẽ dùng câu này làm slogan.
-Tôi là Clang Bang. Hãy đưa tôi năm mươi Shell Credit để nghe kế hoạch trả thù của tôi trong Peaks of Prestige.
-Ghi chú: Câu này được đón nhận tốt. Có lẽ tôi nên viết thêm vài câu theo phong cách này...
-Ghi chú bổ sung: Một khi Peaks of Prestige thực sự kiếm được tiền, tôi nhất định sẽ chuyển sang quảng cáo trang trọng hơn...
-&lt;s&gt;Để cứu Peaks of Prestige đang trên bờ vực thất bại, chính tôi, người sáng tạo ra trò chơi, sẽ trực tiếp đảm nhận vai trò chăm sóc khách hàng!&lt;/s&gt;
-Ghi chú: Quá sát thực tế!
-(Dưới đây là thêm một số ghi chú về slogan quảng cáo.)</t>
+          <t>&lt;b&gt;Bản thảo Quảng cáo&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -22953,7 +22943,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Giờ là Thủy Triều High, và tôi nghe nói lũ sinh vật Thủy Triều Đen không phải con mồi dễ xơi đâu. Ngay cả những Tacet Discord thông thường cũng trở nên điên loạn dưới đám Mây Tai Họa… Mọi người ở bãi săn vẫn ổn chứ?</t>
+          <t>Giờ là Thủy Triều Cao, và tôi nghe nói lũ sinh vật Thủy Triều Đen không phải con mồi dễ xơi đâu. Ngay cả những Tacet Discord thông thường cũng trở nên điên loạn dưới đám Mây Tai Họa… Mọi người ở bãi săn vẫn ổn chứ?</t>
         </is>
       </c>
     </row>
@@ -23278,7 +23268,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Không hẳn. Tôi chưa bao giờ được Master Cato công nhận. Và không, tôi không tham gia cuộc săn đó. Lúc đó lão thợ săn đang giúp Augusta, còn tôi thì ở trại dưỡng thương.</t>
+          <t>Không hẳn. Tôi chưa bao giờ được Sư phụ Cato công nhận. Và không, tôi không tham gia cuộc săn đó. Lúc đó lão thợ săn đang giúp Augusta, còn tôi thì ở trại dưỡng thương.</t>
         </is>
       </c>
     </row>
@@ -23473,7 +23463,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Khi cả Septimont nín thở theo dõi cuộc đấu giữa Augusta và Arsinosa, những dấu hiệu của Dark Tide lại xuất hiện trên Cao nguyên. Master Cato một mình tiến vào Vùng Đất Hoang để đối mặt với nó, và không bao giờ trở về.</t>
+          <t>Khi cả Septimont nín thở theo dõi cuộc đấu giữa Augusta và Arsinosa, những dấu hiệu của Dark Tide lại xuất hiện trên Cao nguyên. Sư phụ Cato một mình tiến vào Vùng Đất Hoang để đối mặt với nó, và không bao giờ trở về.</t>
         </is>
       </c>
     </row>
@@ -23538,7 +23528,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Gren đổ lỗi cái chết của Master Cato cho những khiếm khuyết cố hữu trong hệ thống hậu cần và hỗ trợ của Cao nguyên. Hắn truy nguyên thất bại ấy về những thỏa hiệp của vị Ephor tiền nhiệm với giới quý tộc. Và thế là cả đội của hắn đã rút khỏi hàng ngũ Võ sĩ.</t>
+          <t>Gren đổ lỗi cái chết của Sư phụ Cato cho những khiếm khuyết cố hữu trong hệ thống hậu cần và hỗ trợ của Cao nguyên. Hắn truy nguyên thất bại ấy về những thỏa hiệp của vị Ephor tiền nhiệm với giới quý tộc. Và thế là cả đội của hắn đã rút khỏi hàng ngũ Võ sĩ.</t>
         </is>
       </c>
     </row>
@@ -23603,7 +23593,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>...Nhìn cái mặt đó làm gì, Champion? Ngươi tưởng ta sẽ gục ngã à? Ngoài đánh nhau ra, ta chỉ giỏi sống sót hơn bạn bè mình thôi.</t>
+          <t>...Nhìn cái mặt đó làm gì, Quán Quân? Mày tưởng tao sẽ gục ngã à? Ngoài đánh nhau ra, tao chỉ giỏi sống sót hơn bạn bè mình thôi.</t>
         </is>
       </c>
     </row>
@@ -23668,7 +23658,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Ta mơ thấy lũ quái Dark Tide tấn công làng. Không có viện binh. Chỉ có hai Gladiator chống đỡ. Khi lũ quái sắp giết ta, một Gladiator đã bế ta lên và chạy.</t>
+          <t>Tao mơ thấy lũ quái Dark Tide tấn công làng. Không có viện binh. Chỉ có hai Gladiator chống đỡ. Khi lũ quái sắp giết tao, một Gladiator đã bế tao lên và chạy.</t>
         </is>
       </c>
     </row>
@@ -23938,7 +23928,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Ta cá là đầu ngươi đang đầy câu hỏi—"Mối quan hệ giữa ngươi với Aeolus là gì?" "Tại sao ngươi lại cố ngăn cậu ta trở thành Gladiator?" "Rolla thực sự có phải là người nhà của cậu ta không?"</t>
+          <t>Tao cá là đầu mày đang đầy câu hỏi—"Mối quan hệ giữa mày với Aeolus là gì?" "Tại sao mày lại cố ngăn cậu ta trở thành Gladiator?" "Rolla thực sự có phải là người nhà của cậu ta không?"</t>
         </is>
       </c>
     </row>
@@ -24653,7 +24643,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Acolyte Phoebe, tôi đã tổng hợp danh sách các Acolyte mất tích từ Xưởng Dệt Vải dưới vực sâu. Acolyte Luther trông cậy vào cô để điều phối phản ứng đấy.</t>
+          <t>Tín Đồ Phoebe, tôi đã tổng hợp danh sách các Tín Đồ mất tích từ Xưởng Dệt Vải dưới vực sâu. Tín Đồ Luther trông cậy vào cô để điều phối phản ứng đấy.</t>
         </is>
       </c>
     </row>
@@ -24783,7 +24773,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Đợi đã... Cậu là một trong những tên đòi nợ à? Nghe này, ta là cố vấn tài chính chuyên nghiệp! Dù Đại úy Brant nợ cậu gì đi nữa, không có giấy nợ chính thức thì không có hiệu lực đâu!</t>
+          <t>Đợi đã... Cậu là một trong những tên đòi nợ à? Nghe này, tao là cố vấn tài chính chuyên nghiệp! Dù Đại úy Brant nợ cậu gì đi nữa, không có giấy nợ chính thức thì không có hiệu lực đâu!</t>
         </is>
       </c>
     </row>
@@ -24848,7 +24838,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>À, tôi nhớ ra rồi! Chị chắc hẳn là cô Lenore từ... từ Cục Archive Vụ Sự Vụ Thánh Địa gì đó phải không? Chị đã gửi thư động viên sau khi tôi xin hỗ trợ từ Hội.</t>
+          <t>À, tôi nhớ ra rồi! Chị chắc hẳn là cô Lenore từ... từ Cục Lưu Trữ Vụ Sự Vụ Thánh Địa gì đó phải không? Chị đã gửi thư động viên sau khi tôi xin hỗ trợ từ Hội.</t>
         </is>
       </c>
     </row>
@@ -25953,7 +25943,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Chào mọi người, tên ta là Lenore, thuộc Kho Archive Cấm Phụ của Dòng Trật Tự Vực Sâu. À, xin lỗi, giờ ta thuộc về Xưởng Dệt Vực Sâu… Không, chắc cũng không phải thế…</t>
+          <t>Chào mọi người, tên ta là Lenore, thuộc Kho Lưu Trữ Cấm Phụ của Dòng Trật Tự Vực Sâu. À, xin lỗi, giờ ta thuộc về Xưởng Dệt Vực Sâu… Không, chắc cũng không phải thế…</t>
         </is>
       </c>
     </row>
@@ -26018,7 +26008,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Chúng ta từng sợ hãi những hiểm nguy ngoài làn sương biển, rồi quay sang nghi ngờ và kiêu ngạo với đồng bào Rinascita. Cho đến khi chúng ta vươn tay ra và tìm lại được ý nghĩa thực sự của Sự Unity.</t>
+          <t>Chúng ta từng sợ hãi những hiểm nguy ngoài làn sương biển, rồi quay sang nghi ngờ và kiêu ngạo với đồng bào Rinascita. Cho đến khi chúng ta vươn tay ra và tìm lại được ý nghĩa thực sự của Sự Đoàn Kết.</t>
         </is>
       </c>
     </row>
@@ -26148,7 +26138,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Từng có lúc ta sợ hãi vai trò của một Acolyte. Ta lo rằng những giáo lý về Cứu Rỗi, Thống Nhất và Thăng Hoa có thể lại bị Threnody bóp méo để triệu hồi Hắc Triều.</t>
+          <t>Từng có lúc ta sợ hãi vai trò của một Tín Đồ. Ta lo rằng những giáo lý về Cứu Rỗi, Thống Nhất và Thăng Hoa có thể lại bị Threnody bóp méo để triệu hồi Hắc Triều.</t>
         </is>
       </c>
     </row>
@@ -26928,7 +26918,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Họ gọi đó là Sự Cứu Rỗi và Unity, nhưng thực chất chỉ là bước rơi xuống vực thẳm! Một lời dối trá trống rỗng, tước đoạt ý chí của con người. Hội Đồng hứa hẹn Sự Thăng Hoa, nhưng chính họ đã chìm sâu trong Biển Hắc Ám mà họ tuyên bố sẽ vượt qua!</t>
+          <t>Họ gọi đó là Sự Cứu Rỗi và Đoàn Kết, nhưng thực chất chỉ là bước rơi xuống vực thẳm! Một lời dối trá trống rỗng, tước đoạt ý chí của con người. Hội Đồng hứa hẹn Sự Thăng Hoa, nhưng chính họ đã chìm sâu trong Biển Hắc Ám mà họ tuyên bố sẽ vượt qua!</t>
         </is>
       </c>
     </row>
@@ -27383,7 +27373,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Qiuyuan chiến đấu một mình, đẩy lùi lũ Tidespawn trên đường phố và giải cứu một Tu Sĩ đang sơ tán dân thường. Carlotta cùng đồng đội sớm đến trợ giúp, hướng dẫn dân chúng tìm nơi trú ẩn tại Cathedral of Mercury và Averardo Vault. Vì Qiuyuan không đến từ Rinascita, Thủy Triều Hắc Ám không làm hại ông. Thay vào đó, nó cho phép ông cảm nhận được cậu đang truy đuổi Galbrena ở nơi xa xôi, Avinoleum...</t>
+          <t>Qiuyuan chiến đấu một mình, đẩy lùi lũ Tidespawn trên đường phố và giải cứu một Tu Sĩ đang sơ tán dân thường. Carlotta cùng đồng đội sớm đến trợ giúp, hướng dẫn dân chúng tìm nơi trú ẩn tại Nhà Thờ Mercury và Hầm Averardo. Vì Qiuyuan không đến từ Rinascita, Thủy Triều Hắc Ám không làm hại ông. Thay vào đó, nó cho phép ông cảm nhận được cậu đang truy đuổi Galbrena ở nơi xa xôi, Avinoleum...</t>
         </is>
       </c>
     </row>
@@ -27448,7 +27438,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Tôi đã từng có cơ hội gặp gỡ nhiều quan chức cấp cao ở Mingting. &lt;te href=260002&gt;Ministry of Sentinel Affairs&lt;/te&gt; từng giới thiệu tôi về cách vận hành của &lt;te href=260001&gt;Cơ Quan An Ninh Nội Bộ&lt;/te&gt; của các cậu.</t>
+          <t>Tôi đã từng có cơ hội gặp gỡ nhiều quan chức cấp cao ở Minh Đình. &lt;te href=260002&gt;Bộ Sự Vụ Cảnh Vệ&lt;/te&gt; từng giới thiệu tôi về cách vận hành của &lt;te href=260001&gt;Cơ Quan An Ninh Nội Bộ&lt;/te&gt; của các cậu.</t>
         </is>
       </c>
     </row>
@@ -27578,7 +27568,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Qiuyuan đến Avinoleum khi ấy. Cartethyia đã bị Galbrena giết hại, còn cậu thì đã rời đi truy đuổi hắn. Chỉ còn Cantarella ở lại. Cô nhận ra Qiuyuan từng là quan cao cấp của Mingting. Ông nói có người ở Mingting đã phái ông đến trợ giúp cậu, và qua khả năng Mindsight, ông nhận thấy Dấu Ấn Thủy Triều Hắc Ám đang bám lấy cậu...</t>
+          <t>Qiuyuan đến Avinoleum khi ấy. Cartethyia đã bị Galbrena giết hại, còn cậu thì đã rời đi truy đuổi hắn. Chỉ còn Cantarella ở lại. Cô nhận ra Qiuyuan từng là quan cao cấp của Minh Đình. Ông nói có người ở Minh Đình đã phái ông đến trợ giúp cậu, và qua khả năng Mindsight, ông nhận thấy Dấu Ấn Thủy Triều Hắc Ám đang bám lấy cậu...</t>
         </is>
       </c>
     </row>
@@ -27643,7 +27633,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Theo manh mối của Cantarella, Qiuyuan tìm thấy Fenrico tại Xưởng Dệt Sâu, nhưng bị chặn lại bởi ảo ảnh của một Acolyte – thực chất là thành viên của Fractsidus cải trang. Qiuyuan lập tức nhận ra "hắn" chính là kẻ đã sát hại Sư Phụ của mình. Nhưng cậu cũng biết đây chỉ là một ảo ảnh, không phải "thủ phạm" thật sự. Người đàn ông đó tuyên bố sẽ không ngăn cản Qiuyuan và bước sang một bên, chỉ nói rằng số phận của Fenrico sẽ được hoàn thành nếu cậu được đi qua...</t>
+          <t>Theo manh mối của Cantarella, Qiuyuan tìm thấy Fenrico tại Xưởng Dệt Sâu, nhưng bị chặn lại bởi ảo ảnh của một Tín Đồ – thực chất là thành viên của Fractsidus cải trang. Qiuyuan lập tức nhận ra "hắn" chính là kẻ đã sát hại Sư Phụ của mình. Nhưng cậu cũng biết đây chỉ là một ảo ảnh, không phải "thủ phạm" thật sự. Người đàn ông đó tuyên bố sẽ không ngăn cản Qiuyuan và bước sang một bên, chỉ nói rằng số phận của Fenrico sẽ được hoàn thành nếu cậu được đi qua...</t>
         </is>
       </c>
     </row>
@@ -27773,7 +27763,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Nhưng cuối cùng... tín điều đó đã nuốt chửng tôi. Tôi tin mình có thể dùng Leviathan như một chiếc búa để rèn nên một Land Phúc Ân đích thực, chống lại "Thiên Đường" rỗng tuếch của Nó. Nhưng chính tôi mới là kẻ bị lợi dụng.</t>
+          <t>Nhưng cuối cùng... tín điều đó đã nuốt chửng tôi. Tôi tin mình có thể dùng Leviathan như một chiếc búa để rèn nên một Vùng Đất Phúc Ân đích thực, chống lại "Thiên Đường" rỗng tuếch của Nó. Nhưng chính tôi mới là kẻ bị lợi dụng.</t>
         </is>
       </c>
     </row>
@@ -27903,7 +27893,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Qiuyuan từng đối mặt với một lựa chọn khó khăn. Theo lệnh của Ngự Sử Đài Mingting, ông phải giết chết Geshu Lin, nhưng ông đã do dự khi thấy người đàn ông ấy chưa hoàn toàn sa ngã. Ông nhìn thấy ngọn lửa cuồng nộ trong tim Geshu Lin, nhưng như lời thầy mình từng dạy, ông đã khuyên Geshu Lin kiềm chế sức mạnh của mình. Bằng cách bất tuân lệnh Ngự Sử Đài, ông đã tha mạng cho Geshu Lin.</t>
+          <t>Qiuyuan từng đối mặt với một lựa chọn khó khăn. Theo lệnh của Ngự Sử Đài Minh Đình, ông phải giết chết Geshu Lin, nhưng ông đã do dự khi thấy người đàn ông ấy chưa hoàn toàn sa ngã. Ông nhìn thấy ngọn lửa cuồng nộ trong tim Geshu Lin, nhưng như lời thầy mình từng dạy, ông đã khuyên Geshu Lin kiềm chế sức mạnh của mình. Bằng cách bất tuân lệnh Ngự Sử Đài, ông đã tha mạng cho Geshu Lin.</t>
         </is>
       </c>
     </row>
@@ -28293,7 +28283,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Ví dụ, chắc cậu cũng từng thấy Etheric Sea ở Huanglong rồi nhỉ? Đó là một hiện tượng bầu trời độc đáo, gắn liền với sự xuất hiện của Tacet Field và Tacet Discord.</t>
+          <t>Ví dụ, chắc cậu cũng từng thấy Biển Ether ở Huanglong rồi nhỉ? Đó là một hiện tượng bầu trời độc đáo, gắn liền với sự xuất hiện của Tổ Tacet và Tacet Discord.</t>
         </is>
       </c>
     </row>
@@ -28423,7 +28413,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Nhà vô địch hiện tại cũng là Người Chiến Thắng của Ragunna, {Male=anh ấy;Female=cô ấy} từng chiến đấu bên cạnh Thánh Nữ và các chiến binh khác chống lại Bóng Tối Tràn Về.</t>
+          <t>Nhà vô địch hiện tại cũng là Người Chiến Thắng của Ragunna, {Male=he;Female=she} từng chiến đấu bên cạnh Thánh Nữ và các chiến binh khác chống lại Bóng Tối Tràn Về.</t>
         </is>
       </c>
     </row>
@@ -28683,7 +28673,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Ta vừa nghĩ ra ý tưởng cho kịch bản tiếp theo. Cứ tưởng tượng này: Thủy Triều Đen trỗi dậy, và đó là lúc mọi người nhận ra Người Bảo Vệ đã thực sự biến mất. Hoảng loạn lan tràn, tín đồ gần như bị xóa sổ.</t>
+          <t>Tao vừa nghĩ ra ý tưởng cho kịch bản tiếp theo. Cứ tưởng tượng này: Thủy Triều Đen trỗi dậy, và đó là lúc mọi người nhận ra Người Bảo Vệ đã thực sự biến mất. Hoảng loạn lan tràn, tín đồ gần như bị xóa sổ.</t>
         </is>
       </c>
     </row>
@@ -28813,7 +28803,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Place Bọ Hung Goldcrest vào chiếc bánh nướng làm từ Mastic Nuvola và Viscum Berry... rồi nhẹ nhàng đặt vào vỏ Bell Crab, sắp xếp sao cho giống cử động tinh nghịch của con bọ...</t>
+          <t>Đặt Bọ Hung Goldcrest vào chiếc bánh nướng làm từ Mastic Nuvola và Viscum Berry... rồi nhẹ nhàng đặt vào vỏ Cua Chuông, sắp xếp sao cho giống cử động tinh nghịch của con bọ...</t>
         </is>
       </c>
     </row>
@@ -29073,7 +29063,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Dodgem vào một đồng Monnaie, đặt câu hỏi với tấm lòng chân thành, và ngươi sẽ nhận được câu trả lời mình cần: dù là tương lai đang chờ đón hay sự thật về quá khứ ngươi tìm kiếm.</t>
+          <t>Ném vào một đồng Monnaie, đặt câu hỏi với tấm lòng chân thành, và ngươi sẽ nhận được câu trả lời mình cần: dù là tương lai đang chờ đón hay sự thật về quá khứ ngươi tìm kiếm.</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29128,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Hãy tôn trọng nghi thức và điều cấm kỵ của Giáo Đoàn. Không gây ồn ào, đánh nhau hay bất kỳ hành vi nào không phù hợp hoặc vượt giới hạn trong Cathedral of Mercury.</t>
+          <t>Hãy tôn trọng nghi thức và điều cấm kỵ của Giáo Đoàn. Không gây ồn ào, đánh nhau hay bất kỳ hành vi nào không phù hợp hoặc vượt giới hạn trong Nhà Thờ Mercury.</t>
         </is>
       </c>
     </row>
@@ -29853,7 +29843,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Nhưng Hội đồng Biên tập có quy trình thẩm định điên rồ lắm. Cậu phải đề xuất dự án phù hợp với sứ mệnh của Hiệp hội, tổ chức chụp ảnh, xin phê duyệt, rồi mới được xuất bản.</t>
+          <t>Nhưng Hội đồng Biên tập có quy trình thẩm định điên rồ lắm. Mày phải đề xuất dự án phù hợp với sứ mệnh của Hiệp hội, tổ chức chụp ảnh, xin phê duyệt, rồi mới được xuất bản.</t>
         </is>
       </c>
     </row>
@@ -29983,7 +29973,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Con phố ngầm này từng là trái tim của giới nghệ thuật Honami. Nơi đây luôn tổ chức liên hoan phim và triển lãm ảnh... Thậm chí ta còn từng trưng bày vài tác phẩm của mình ở đây.</t>
+          <t>Con phố ngầm này từng là trái tim của giới nghệ thuật Honami. Nơi đây luôn tổ chức liên hoan phim và triển lãm ảnh... Thậm chí tao còn từng trưng bày vài tác phẩm của mình ở đây.</t>
         </is>
       </c>
     </row>
@@ -30511,7 +30501,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Lúc ta mới trở thành Eye, Sander và Lyla còn là hai đứa nhóc mặt non choẹt, tính toán năm chữ số còn lúng túng. Giờ thì chúng đã trưởng thành nhiều, nhưng vẫn cãi nhau như vịt con, haha.</t>
+          <t>Lúc tao mới trở thành Eye, Sander và Lyla còn là hai đứa nhóc mặt non choẹt, tính toán năm chữ số còn lúng túng. Giờ thì chúng đã trưởng thành nhiều, nhưng vẫn cãi nhau như vịt con, haha.</t>
         </is>
       </c>
     </row>
@@ -30706,7 +30696,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Helios trên bầu trời giờ đây kết nối tri thức từ cả Spacetrek Collective lẫn Roya. Những dữ liệu từng chỉ Heliogyre mới thấy... nay Máy Dò Hyvatia cũng có thể thu thập.</t>
+          <t>Helios trên bầu trời giờ đây kết nối tri thức từ cả Tập Đoàn Spacetrek lẫn Roya. Những dữ liệu từng chỉ Heliogyre mới thấy... nay Máy Dò Hyvatia cũng có thể thu thập.</t>
         </is>
       </c>
     </row>
@@ -30966,7 +30956,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Yet... Spacetrek Collective đã tìm cách chữa trị. Giống như Heliodic Six với sức mạnh phàm trần đã chạm tới thần thánh, công nghệ của họ cũng đang nỗ lực hóa giải cái giá mà các vị thần đã bắt ta phải trả.</t>
+          <t>Dù vậy... Spacetrek Collective đã tìm cách chữa trị. Giống như Heliodic Six với sức mạnh phàm trần đã chạm tới thần thánh, công nghệ của họ cũng đang nỗ lực hóa giải cái giá mà các vị thần đã bắt ta phải trả.</t>
         </is>
       </c>
     </row>
@@ -31096,7 +31086,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Mọi thứ thay đổi vào ngày cơn Void Storm ấy. Khi bầu trời sáng trở lại, một Soliskin đã tìm thấy chúng tôi. Chúng tôi theo nó vào Bjartr Woods, và ở đó, chúng tôi tìm thấy Yngvar, bất tỉnh.</t>
+          <t>Mọi thứ thay đổi vào ngày cơn Bão Hư Không ấy. Khi bầu trời sáng trở lại, một Soliskin đã tìm thấy chúng tôi. Chúng tôi theo nó vào Bjartr Woods, và ở đó, chúng tôi tìm thấy Yngvar, bất tỉnh.</t>
         </is>
       </c>
     </row>
@@ -31226,7 +31216,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Hỡi Rover được thủy triều dẫn lối, ngươi đã chinh phục những đỉnh cao của Jinzhou và lắng nghe sóng vỗ vào Bờ Đen. Ngươi đã vượt qua bão tố, nghe thấy hai mặt đức tin của Ragunna, và nếm trải vinh quang trong đấu trường Septimont. Giờ đây, con đường đến vùng biên giới băng giá mở ra tại Honami City. Đã đến lúc lên đường đến Lahai-Roi.</t>
+          <t>Hỡi Vận Mệnh Giả được thủy triều dẫn lối, ngươi đã chinh phục những đỉnh cao của Jinzhou và lắng nghe sóng vỗ vào Bờ Đen. Ngươi đã vượt qua bão tố, nghe thấy hai mặt đức tin của Ragunna, và nếm trải vinh quang trong đấu trường Septimont. Giờ đây, con đường đến vùng biên giới băng giá mở ra tại Thành phố Honami. Đã đến lúc lên đường đến Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -31291,7 +31281,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Tại Tấn Châu, cậu đã cùng Jiyan và Resonators khác dập tắt đợt bùng phát Discord ở vùng Norfall Barrens. Cậu cũng đã gặp "bé Abby" ở đó. Cuối cùng, các cậu đã chiến thắng và hấp thụ được Dreamless.</t>
+          <t>Tại Tấn Châu, cậu đã cùng Jiyan và các Resonator khác dập tắt đợt bùng phát Tacet Discord ở vùng Norfall Barrens. Cậu cũng đã gặp "bé Abby" ở đó. Cuối cùng, các cậu đã chiến thắng và hấp thụ được Dreamless.</t>
         </is>
       </c>
     </row>
@@ -31486,7 +31476,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Khi Hội Ám Muội âm mưu phá hoại Lễ Hội Carnevale, ngươi và đồng đội đã xoa dịu cơn thịnh nộ của Lorelei, đánh bại Dragon Than Khóc, rồi liên thủ cùng Đoàn Kẻ Ngốc để thổi hồn vào lễ hội.</t>
+          <t>Khi Hội Ám Muội âm mưu phá hoại Lễ Hội Carnevale, ngươi và đồng đội đã xoa dịu cơn thịnh nộ của Lorelei, đánh bại Rồng Than Khóc, rồi liên thủ cùng Đoàn Kẻ Ngốc để thổi hồn vào lễ hội.</t>
         </is>
       </c>
     </row>
@@ -31681,7 +31671,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Theo lời mời của Cantarella, tộc trưởng gia tộc Fisalia, cậu đã đến Lâu đài Porto-Veno. Từ bà, cậu biết được "Leviathan" của Threnodian sở hữu sức mạnh hợp nhất và đồng hóa.</t>
+          <t>Theo lời mời của Cantarella, tộc trưởng gia tộc Fisalia, cậu đã đến Porto-Veno Castle. Từ bà, cậu biết được "Leviathan" của Threnodian sở hữu sức mạnh hợp nhất và đồng hóa.</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32256,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Tại Sanguis Plateaus, ngươi đã gặp Avidius, một Hero of Heroes được Senate công nhận. Trong cuộc truy đuổi cuối cùng của sinh vật Bóng Tối tên Corrosaurus, Augusta chuẩn bị thực hiện kế hoạch ban đầu của mình—</t>
+          <t>Tại Cao Nguyên Sanguis, ngươi đã gặp Avidius, một Anh Hùng Trong Các Anh Hùng được Thượng Nghị Viện công nhận. Trong cuộc truy đuổi cuối cùng của sinh vật Bóng Tối tên Corrosaurus, Augusta chuẩn bị thực hiện kế hoạch ban đầu của mình—</t>
         </is>
       </c>
     </row>
@@ -32331,7 +32321,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Để xoay chuyển cục diện, Iuno đã hy sinh chính sự tồn tại của mình, buộc Echo phải hiện hình dưới dạng Dark Tide, trao cho cậu và Augusta cơ hội cuối cùng để đánh bại Kẻ Giả Mạo. Vượt qua mọi dự đoán, các cậu đã chiến thắng.</t>
+          <t>Để xoay chuyển cục diện, Iuno đã hy sinh chính sự tồn tại của mình, buộc Tổ Tacet phải hiện hình dưới dạng Dark Tide, trao cho cậu và Augusta cơ hội cuối cùng để đánh bại Kẻ Giả Mạo. Vượt qua mọi dự đoán, các cậu đã chiến thắng.</t>
         </is>
       </c>
     </row>
@@ -32396,7 +32386,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Quyết tâm đưa Iuno trở lại, cậu đã đến Tetragon Temple tìm kiếm manh mối. Qua câu chuyện của Avidius, cậu hiểu rằng sự tồn tại chính là tổng hòa của ký ức, cảm xúc và những mối liên kết. Cậu quyết định Neo giữ Iuno trở lại hiện thực thông qua những sợi dây gắn bó ấy.</t>
+          <t>Quyết tâm đưa Iuno trở lại, cậu đã đến Đền Tetragon tìm kiếm manh mối. Qua câu chuyện của Avidius, cậu hiểu rằng sự tồn tại chính là tổng hòa của ký ức, cảm xúc và những mối liên kết. Cậu quyết định Neo giữ Iuno trở lại hiện thực thông qua những sợi dây gắn bó ấy.</t>
         </is>
       </c>
     </row>
@@ -32786,7 +32776,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Sau khi kết thúc hành trình ở Rinascita, cậu trở về Black Shores. Tại đó, một vết nứt gần bờ biển đã kéo cậu vào một Sonoro Sphere chứa đựng tàn tích của thành phố Honami từng một thời phồn thịnh.</t>
+          <t>Sau khi kết thúc hành trình ở Rinascita, cậu trở về Bờ Biển Đen. Tại đó, một vết nứt gần bờ biển đã kéo cậu vào một Sonoro Sphere chứa đựng tàn tích của thành phố Honami từng một thời phồn thịnh.</t>
         </is>
       </c>
     </row>
